--- a/request_forms/035_media_folder_creation_request--request_forms.xlsx
+++ b/request_forms/035_media_folder_creation_request--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>request_form_version</t>
+          <t>request_form_version_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Request Form Version</t>
+          <t>Request Form Version 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>request_form_submitter</t>
+          <t>request_form_submitter_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Request Form Submitter</t>
+          <t>Request Form Submitter 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>submitter_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>Submitter 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>team_members</t>
+          <t>team_members_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Team Members 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_submitter</t>
+          <t>form_submitter_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Form Submitter</t>
+          <t>Form Submitter 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>request_form_version</t>
+          <t>request_form_version_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Request Form Version</t>
+          <t>Request Form Version 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>media_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,148 +1182,250 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>request_status_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>request_status_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_choices</t>
+          <t>request_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>request_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>request_status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>team_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>team_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>team_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>team_members_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>team_members_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>team_members_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
